--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 270-2025</t>
+          <t>A 24088-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -702,14 +702,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45660</v>
+        <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>8.9</v>
+        <v>2.8</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -761,152 +761,152 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Tusengömming
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 270-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45660</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SOTENÄS</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsalm
 Skogsödla</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 24088-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45795</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SOTENÄS</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Tusengömming
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 50239-2022</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44865</v>
+        <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>13.2</v>
+        <v>30.3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -945,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -963,55 +963,55 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46038</v>
+        <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>14.1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1081,42 +1081,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,16 +1146,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>30.3</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1179,49 +1179,49 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 50239-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45795</v>
+        <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1251,20 +1251,20 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.1</v>
+        <v>13.2</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45415</v>
+        <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7.7</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1489,7 +1489,7 @@
         <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45582</v>
+        <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45582</v>
+        <v>44867</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1701,14 +1701,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45477</v>
+        <v>45795</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45956</v>
+        <v>45596</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>45327</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46157</v>
+        <v>45956</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45637</v>
+        <v>45582</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44592</v>
+        <v>45477</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45596</v>
+        <v>46157</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45596</v>
+        <v>46272</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46272</v>
+        <v>44592</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45582</v>
+        <v>45415</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>7.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45415</v>
+        <v>45582</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44867</v>
+        <v>45477</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2650,14 +2650,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45795</v>
+        <v>45596</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 24088-2025</t>
+          <t>A 270-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -702,14 +702,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45795</v>
+        <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.8</v>
+        <v>8.9</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -761,152 +761,152 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsalm
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 24088-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45795</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SOTENÄS</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Ask
 Tusengömming
 Blåsippa</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 270-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45660</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SOTENÄS</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsalm
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 50239-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45795</v>
+        <v>44865</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>30.3</v>
+        <v>13.2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -945,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -963,55 +963,55 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>14.1</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1081,42 +1081,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46038</v>
+        <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,17 +1146,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>30.3</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1179,49 +1179,49 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50239-2022</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44865</v>
+        <v>45795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45637</v>
+        <v>45415</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1489,7 +1489,7 @@
         <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45415</v>
+        <v>45582</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.2</v>
+        <v>2.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44867</v>
+        <v>45582</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1701,14 +1701,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45795</v>
+        <v>45637</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45596</v>
+        <v>44592</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45327</v>
+        <v>45956</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45956</v>
+        <v>45596</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45582</v>
+        <v>45477</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45477</v>
+        <v>46157</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46157</v>
+        <v>45327</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46272</v>
+        <v>45596</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44592</v>
+        <v>45582</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45415</v>
+        <v>46272</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45582</v>
+        <v>45477</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45582</v>
+        <v>45415</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>6.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45477</v>
+        <v>44867</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2650,14 +2650,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45596</v>
+        <v>45795</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45795</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 50239-2022</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44865</v>
+        <v>46038</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>13.2</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -960,10 +960,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -976,42 +976,42 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 50239-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46038</v>
+        <v>44865</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,20 +1041,20 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>13.2</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
@@ -1065,10 +1065,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1081,35 +1081,35 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>45795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45415</v>
+        <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7.7</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1489,7 +1489,7 @@
         <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1628,14 +1628,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45582</v>
+        <v>45795</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45637</v>
+        <v>45327</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44592</v>
+        <v>45956</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45956</v>
+        <v>45582</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45596</v>
+        <v>45477</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45477</v>
+        <v>44592</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         <v>46157</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45327</v>
+        <v>45415</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45596</v>
+        <v>45582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2292,7 +2292,7 @@
         <v>45582</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46272</v>
+        <v>45477</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45477</v>
+        <v>45596</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45415</v>
+        <v>46272</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.2</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44867</v>
+        <v>45415</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2650,14 +2650,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45795</v>
+        <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45795</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 50239-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46038</v>
+        <v>44865</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,20 +936,20 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>13.2</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
@@ -960,10 +960,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -976,42 +976,42 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 50239-2022</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44865</v>
+        <v>46038</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>13.2</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1065,10 +1065,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1081,35 +1081,35 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>45795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45637</v>
+        <v>45415</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1489,7 +1489,7 @@
         <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45596</v>
+        <v>45582</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1628,14 +1628,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45795</v>
+        <v>45582</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45327</v>
+        <v>45477</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.5</v>
+        <v>0.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45956</v>
+        <v>45327</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45582</v>
+        <v>46157</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45477</v>
+        <v>45956</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44592</v>
+        <v>46272</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46157</v>
+        <v>45637</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45415</v>
+        <v>44592</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.7</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45596</v>
+        <v>45477</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46272</v>
+        <v>45415</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>6.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45415</v>
+        <v>44867</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2650,14 +2650,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44867</v>
+        <v>45795</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45795</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44865</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>46038</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>45795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45415</v>
+        <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7.7</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1489,7 +1489,7 @@
         <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45582</v>
+        <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45327</v>
+        <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46157</v>
+        <v>45956</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45956</v>
+        <v>46157</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46272</v>
+        <v>44592</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45637</v>
+        <v>45415</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44592</v>
+        <v>45582</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45596</v>
+        <v>45582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45596</v>
+        <v>45477</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45477</v>
+        <v>46272</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2511,7 +2511,7 @@
         <v>45415</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>44867</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>45795</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45795</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44865</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>46038</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>45795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>45596</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45956</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>46157</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>44592</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>45415</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45582</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45477</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>46272</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45415</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>44867</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>45795</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45795</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44865</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>46038</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>45795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>45596</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45956</v>
+        <v>46157</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46157</v>
+        <v>45956</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>44592</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>45415</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45582</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45477</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>46272</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45415</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>44867</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>45795</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45795</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44865</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46038</v>
+        <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,17 +1041,17 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>30.3</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1074,49 +1074,49 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,16 +1146,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>30.3</v>
+        <v>14.1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1179,49 +1179,49 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.1</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45637</v>
+        <v>45477</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45477</v>
+        <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>7.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45596</v>
+        <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45327</v>
+        <v>44867</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45582</v>
+        <v>45327</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46157</v>
+        <v>45582</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45956</v>
+        <v>45582</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1993,14 +1993,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44592</v>
+        <v>45795</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45415</v>
+        <v>45956</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.7</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45582</v>
+        <v>45637</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45582</v>
+        <v>44592</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45477</v>
+        <v>45596</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2365,7 +2365,7 @@
         <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46272</v>
+        <v>45582</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45415</v>
+        <v>45477</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44867</v>
+        <v>46157</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2650,14 +2650,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45795</v>
+        <v>46272</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45795</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44865</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,16 +1041,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>30.3</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1074,49 +1074,49 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,17 +1146,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>14.1</v>
+        <v>30.3</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1179,49 +1179,49 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46038</v>
+        <v>45795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>14.1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45477</v>
+        <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45415</v>
+        <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7.7</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45415</v>
+        <v>45596</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44867</v>
+        <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45327</v>
+        <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45582</v>
+        <v>45956</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45582</v>
+        <v>46157</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1993,14 +1993,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45795</v>
+        <v>44592</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45956</v>
+        <v>45415</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>7.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45637</v>
+        <v>45582</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44592</v>
+        <v>45582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45596</v>
+        <v>45477</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2365,7 +2365,7 @@
         <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45582</v>
+        <v>46272</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45477</v>
+        <v>45415</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46157</v>
+        <v>44867</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2650,14 +2650,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46272</v>
+        <v>45795</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 270-2025</t>
+          <t>A 24088-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -702,14 +702,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45660</v>
+        <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>8.9</v>
+        <v>2.8</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -761,152 +761,152 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Tusengömming
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 270-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45660</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SOTENÄS</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsalm
 Skogsödla</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 24088-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45795</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SOTENÄS</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Tusengömming
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 50239-2022</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44865</v>
+        <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>13.2</v>
+        <v>30.3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -945,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -963,55 +963,55 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46038</v>
+        <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>14.1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1081,42 +1081,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,16 +1146,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>30.3</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1179,49 +1179,49 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 50239-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45795</v>
+        <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1251,20 +1251,20 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.1</v>
+        <v>13.2</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45637</v>
+        <v>45415</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45477</v>
+        <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45596</v>
+        <v>44867</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45327</v>
+        <v>45477</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1708,7 +1708,7 @@
         <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>45956</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1920,14 +1920,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46157</v>
+        <v>45795</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44592</v>
+        <v>45477</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45415</v>
+        <v>46157</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.7</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45582</v>
+        <v>45327</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45582</v>
+        <v>46272</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45477</v>
+        <v>45637</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45596</v>
+        <v>44592</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46272</v>
+        <v>45596</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45415</v>
+        <v>45596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44867</v>
+        <v>45582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2650,14 +2650,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45795</v>
+        <v>45477</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45660</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>46038</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45415</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44867</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>45477</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45956</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45795</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45477</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>46157</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45327</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>46272</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45637</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44592</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>45596</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>45477</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45660</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>46038</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45415</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>44867</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>45477</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45956</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45795</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45477</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>46157</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45327</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>46272</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45637</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44592</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>45596</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>45477</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45660</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>46038</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45415</v>
+        <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7.7</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45415</v>
+        <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44867</v>
+        <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45477</v>
+        <v>44867</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1701,14 +1701,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45582</v>
+        <v>45795</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45956</v>
+        <v>45327</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1920,14 +1920,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45795</v>
+        <v>45956</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46157</v>
+        <v>45477</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45327</v>
+        <v>44592</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46272</v>
+        <v>46157</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45637</v>
+        <v>45415</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44592</v>
+        <v>45582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45596</v>
+        <v>45582</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45596</v>
+        <v>45477</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45477</v>
+        <v>46272</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45660</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>46038</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45637</v>
+        <v>45415</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45477</v>
+        <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45415</v>
+        <v>44867</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44867</v>
+        <v>45477</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>45795</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45596</v>
+        <v>45582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45327</v>
+        <v>45582</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1927,7 +1927,7 @@
         <v>45956</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45582</v>
+        <v>45477</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45477</v>
+        <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44592</v>
+        <v>46157</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46157</v>
+        <v>45637</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45415</v>
+        <v>44592</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.7</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45582</v>
+        <v>46272</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45477</v>
+        <v>45596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45596</v>
+        <v>45582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46272</v>
+        <v>45477</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45660</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 50239-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45795</v>
+        <v>44865</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>30.3</v>
+        <v>13.2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -945,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -963,55 +963,55 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1028,7 +1028,7 @@
         <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,17 +1041,17 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>14.1</v>
+        <v>30.3</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1074,49 +1074,49 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46038</v>
+        <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>14.1</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1186,42 +1186,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50239-2022</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44865</v>
+        <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.2</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45415</v>
+        <v>44592</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7.7</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45415</v>
+        <v>45637</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44867</v>
+        <v>45582</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45477</v>
+        <v>45415</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.4</v>
+        <v>7.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1701,14 +1701,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45795</v>
+        <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1781,7 +1781,7 @@
         <v>45582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45582</v>
+        <v>45477</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45956</v>
+        <v>45477</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>45477</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45327</v>
+        <v>45415</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46157</v>
+        <v>44867</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45637</v>
+        <v>45596</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44592</v>
+        <v>45596</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2358,14 +2358,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45596</v>
+        <v>45795</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46272</v>
+        <v>45327</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45596</v>
+        <v>45956</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45582</v>
+        <v>46157</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45477</v>
+        <v>46272</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45660</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 50239-2022</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44865</v>
+        <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>13.2</v>
+        <v>30.3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -945,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -963,55 +963,55 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1028,7 +1028,7 @@
         <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,16 +1041,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>30.3</v>
+        <v>14.1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1074,49 +1074,49 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>14.1</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1186,42 +1186,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 50239-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46038</v>
+        <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1251,20 +1251,20 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>13.2</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44592</v>
+        <v>45415</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45637</v>
+        <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45582</v>
+        <v>45477</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45415</v>
+        <v>44867</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.7</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45477</v>
+        <v>45956</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1920,14 +1920,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45477</v>
+        <v>45795</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>45477</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45415</v>
+        <v>46157</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.2</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44867</v>
+        <v>45327</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45596</v>
+        <v>46272</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45596</v>
+        <v>45637</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2358,14 +2358,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45795</v>
+        <v>44592</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45327</v>
+        <v>45596</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45956</v>
+        <v>45596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46157</v>
+        <v>45582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46272</v>
+        <v>45477</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45660</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,16 +936,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>30.3</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -969,49 +969,49 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1028,7 +1028,7 @@
         <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,17 +1041,17 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>14.1</v>
+        <v>30.3</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1074,49 +1074,49 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46038</v>
+        <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>14.1</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1186,35 +1186,35 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45415</v>
+        <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7.7</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45415</v>
+        <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45477</v>
+        <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.4</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1635,7 +1635,7 @@
         <v>44867</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45582</v>
+        <v>45327</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>45956</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45795</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46157</v>
+        <v>45477</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45327</v>
+        <v>46157</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46272</v>
+        <v>44592</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45637</v>
+        <v>45415</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44592</v>
+        <v>45582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45596</v>
+        <v>45582</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45596</v>
+        <v>46272</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45582</v>
+        <v>45477</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45477</v>
+        <v>45596</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45660</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>46038</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>44867</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>45596</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45327</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45956</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45795</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45582</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>45477</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>46157</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>44592</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45415</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>45582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>45582</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>46272</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45477</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>45596</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45660</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>46038</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>44867</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>45596</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45327</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45956</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45795</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45582</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>45477</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>46157</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>44592</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45415</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>45582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>45582</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>46272</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45477</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>45596</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>45890</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE28"/>
+  <dimension ref="A1:AE29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 24088-2025</t>
+          <t>A 270-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -702,14 +702,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45795</v>
+        <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.8</v>
+        <v>8.9</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -761,152 +761,152 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsalm
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 24088-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45795</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SOTENÄS</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Ask
 Tusengömming
 Blåsippa</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 270-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45660</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SOTENÄS</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsalm
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 50239-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46038</v>
+        <v>44865</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,20 +936,20 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>13.2</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
@@ -960,10 +960,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -976,42 +976,42 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,16 +1041,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>30.3</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1074,49 +1074,49 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,17 +1146,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>14.1</v>
+        <v>30.3</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1179,49 +1179,49 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50239-2022</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44865</v>
+        <v>45795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45637</v>
+        <v>45415</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1489,7 +1489,7 @@
         <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1555,14 +1555,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45415</v>
+        <v>45795</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.2</v>
+        <v>0.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44867</v>
+        <v>45582</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45596</v>
+        <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45327</v>
+        <v>45956</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45956</v>
+        <v>45477</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1920,14 +1920,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45795</v>
+        <v>45327</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45582</v>
+        <v>46157</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45477</v>
+        <v>45637</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46157</v>
+        <v>44592</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44592</v>
+        <v>45596</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45415</v>
+        <v>46272</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2438,7 +2438,7 @@
         <v>45582</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46272</v>
+        <v>45477</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45477</v>
+        <v>45415</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 35770-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45596</v>
+        <v>46264</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2710,83 +2710,156 @@
       </c>
       <c r="V27" s="2" t="inlineStr"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
+          <t>A 50864-2022</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>44867</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SOTENÄS</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>S 2369-2025</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D28" s="1" t="n">
+      <c r="D29" s="1" t="n">
         <v>45890</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F28" t="inlineStr">
+      <c r="E29" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>VÄSTRA GÖTALANDS LÄN</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>SOTENÄS</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45795</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 50239-2022</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44865</v>
+        <v>46038</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>13.2</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -960,10 +960,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -976,42 +976,42 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 50239-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46038</v>
+        <v>44865</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,20 +1041,20 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>13.2</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
@@ -1065,10 +1065,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1081,35 +1081,35 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>45795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45415</v>
+        <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7.7</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1489,7 +1489,7 @@
         <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1555,14 +1555,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45795</v>
+        <v>45596</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45582</v>
+        <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1701,14 +1701,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45582</v>
+        <v>45795</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>45956</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45327</v>
+        <v>46157</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46157</v>
+        <v>45477</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45637</v>
+        <v>44592</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44592</v>
+        <v>46272</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45596</v>
+        <v>45415</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46272</v>
+        <v>45582</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45596</v>
+        <v>45582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45582</v>
+        <v>45477</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45477</v>
+        <v>45596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 35770-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45415</v>
+        <v>46264</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.2</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35770-2026</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46264</v>
+        <v>45415</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>6.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>44867</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 270-2025</t>
+          <t>A 24088-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -702,14 +702,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45660</v>
+        <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>8.9</v>
+        <v>2.8</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -761,152 +761,152 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Tusengömming
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 270-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45660</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SOTENÄS</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsalm
 Skogsödla</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 24088-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45795</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SOTENÄS</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Tusengömming
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 50239-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46038</v>
+        <v>44865</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,20 +936,20 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>13.2</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
@@ -960,10 +960,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -976,42 +976,42 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 50239-2022</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44865</v>
+        <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>13.2</v>
+        <v>30.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1050,10 +1050,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1068,55 +1068,55 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,16 +1146,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>30.3</v>
+        <v>14.1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1179,49 +1179,49 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.1</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45637</v>
+        <v>45477</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45477</v>
+        <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>7.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45596</v>
+        <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45327</v>
+        <v>44867</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1701,14 +1701,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45795</v>
+        <v>45327</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1774,14 +1774,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45956</v>
+        <v>45795</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45582</v>
+        <v>45477</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46157</v>
+        <v>45956</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44592</v>
+        <v>45582</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46272</v>
+        <v>46157</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45415</v>
+        <v>45477</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>7.7</v>
+        <v>0.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45582</v>
+        <v>45637</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45582</v>
+        <v>44592</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45477</v>
+        <v>45596</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2511,7 +2511,7 @@
         <v>45596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35770-2026</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46264</v>
+        <v>45582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45415</v>
+        <v>46272</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.2</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2713,7 +2713,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 35770-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44867</v>
+        <v>46264</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 24088-2025</t>
+          <t>A 270-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -702,14 +702,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45795</v>
+        <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.8</v>
+        <v>8.9</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -761,145 +761,145 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsalm
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 24088-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45795</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SOTENÄS</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Ask
 Tusengömming
 Blåsippa</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 270-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45660</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SOTENÄS</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsalm
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
         <v/>
       </c>
     </row>
@@ -923,7 +923,7 @@
         <v>44865</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,16 +1041,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>30.3</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1074,49 +1074,49 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,17 +1146,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>14.1</v>
+        <v>30.3</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1179,49 +1179,49 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46038</v>
+        <v>45795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>14.1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45477</v>
+        <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45415</v>
+        <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7.7</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45415</v>
+        <v>45596</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44867</v>
+        <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45327</v>
+        <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1774,14 +1774,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45795</v>
+        <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45477</v>
+        <v>45956</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45956</v>
+        <v>44592</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45582</v>
+        <v>45415</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>7.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45582</v>
+        <v>46157</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46157</v>
+        <v>45582</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45637</v>
+        <v>45477</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44592</v>
+        <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45596</v>
+        <v>46272</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45596</v>
+        <v>45415</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>6.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45582</v>
+        <v>44867</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2650,14 +2650,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46272</v>
+        <v>45795</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>46264</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 270-2025</t>
+          <t>A 24088-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -702,14 +702,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45660</v>
+        <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>8.9</v>
+        <v>2.8</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -761,152 +761,152 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Tusengömming
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 270-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45660</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SOTENÄS</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsalm
 Skogsödla</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 24088-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45795</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SOTENÄS</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Tusengömming
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 50239-2022</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44865</v>
+        <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>13.2</v>
+        <v>30.3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -945,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -963,55 +963,55 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46038</v>
+        <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>14.1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1081,42 +1081,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 50239-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45795</v>
+        <v>44865</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>30.3</v>
+        <v>13.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1155,10 +1155,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1173,55 +1173,55 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.1</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45637</v>
+        <v>45415</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45477</v>
+        <v>45327</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
         <v>45596</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45327</v>
+        <v>45582</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45582</v>
+        <v>45477</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1781,7 +1781,7 @@
         <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45956</v>
+        <v>45415</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44592</v>
+        <v>45582</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45415</v>
+        <v>45582</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.7</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46157</v>
+        <v>44867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2139,14 +2139,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45582</v>
+        <v>45795</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45582</v>
+        <v>45956</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2292,7 +2292,7 @@
         <v>45477</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45596</v>
+        <v>45637</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46272</v>
+        <v>44592</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45415</v>
+        <v>45596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.2</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44867</v>
+        <v>46157</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2650,14 +2650,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45795</v>
+        <v>46272</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>46264</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45660</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44865</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45415</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45327</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>45596</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>45582</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>45477</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45415</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45582</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45582</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>44867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45795</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45956</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45477</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>45637</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>44592</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>46157</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>46272</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>46264</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45660</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>44865</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45415</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45327</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>45596</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>45582</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>45477</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45415</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45582</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45582</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>44867</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45795</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45956</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45477</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>45637</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>44592</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>46157</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>46272</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>46264</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45660</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 50239-2022</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44865</v>
+        <v>46038</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>13.2</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1158,7 +1158,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1170,10 +1170,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1186,42 +1186,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 50239-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46038</v>
+        <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1251,20 +1251,20 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>13.2</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45415</v>
+        <v>45956</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7.7</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45327</v>
+        <v>45637</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45596</v>
+        <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45582</v>
+        <v>44867</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45477</v>
+        <v>46272</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1774,14 +1774,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45477</v>
+        <v>45795</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45415</v>
+        <v>45477</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 35770-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45582</v>
+        <v>46264</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44867</v>
+        <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2139,14 +2139,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45795</v>
+        <v>46157</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45956</v>
+        <v>45582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2292,7 +2292,7 @@
         <v>45477</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45637</v>
+        <v>44592</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44592</v>
+        <v>45415</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45596</v>
+        <v>45582</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46157</v>
+        <v>45582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46272</v>
+        <v>45477</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2713,7 +2713,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35770-2026</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46264</v>
+        <v>45596</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45660</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>46038</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45956</v>
+        <v>45415</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>7.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45637</v>
+        <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45415</v>
+        <v>44867</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44867</v>
+        <v>45477</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1701,14 +1701,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46272</v>
+        <v>45795</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1774,14 +1774,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45795</v>
+        <v>45582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 35770-2026</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46264</v>
+        <v>45956</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45596</v>
+        <v>45477</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>46157</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45582</v>
+        <v>45637</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45477</v>
+        <v>44592</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44592</v>
+        <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45415</v>
+        <v>46272</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2584,7 +2584,7 @@
         <v>45582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2657,7 +2657,7 @@
         <v>45477</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 35770-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45596</v>
+        <v>46264</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45660</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 50239-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46038</v>
+        <v>44865</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,20 +1146,20 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>13.2</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
@@ -1170,10 +1170,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1186,42 +1186,42 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50239-2022</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44865</v>
+        <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.2</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1416,7 +1416,7 @@
         <v>45415</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7.7</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45415</v>
+        <v>44867</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1555,14 +1555,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44867</v>
+        <v>45795</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45477</v>
+        <v>45637</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1701,14 +1701,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45795</v>
+        <v>45477</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45582</v>
+        <v>45327</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1927,7 +1927,7 @@
         <v>45956</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45327</v>
+        <v>45477</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2146,7 +2146,7 @@
         <v>46157</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45637</v>
+        <v>44592</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44592</v>
+        <v>45415</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45596</v>
+        <v>45582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46272</v>
+        <v>45582</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45596</v>
+        <v>45477</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45582</v>
+        <v>46272</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45477</v>
+        <v>45596</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>46264</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 24088-2025</t>
+          <t>A 270-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -702,14 +702,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45795</v>
+        <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.8</v>
+        <v>8.9</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -761,152 +761,152 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsalm
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 24088-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45795</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SOTENÄS</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Ask
 Tusengömming
 Blåsippa</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 270-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45660</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SOTENÄS</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsalm
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 50239-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45795</v>
+        <v>44865</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>30.3</v>
+        <v>13.2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -945,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -963,55 +963,55 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1028,7 +1028,7 @@
         <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,17 +1041,17 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>14.1</v>
+        <v>30.3</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1074,49 +1074,49 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 50239-2022</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44865</v>
+        <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1158,7 +1158,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1170,10 +1170,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1186,35 +1186,35 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1409,14 +1409,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45415</v>
+        <v>45795</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6.2</v>
+        <v>0.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44867</v>
+        <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>7.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1555,14 +1555,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45795</v>
+        <v>45327</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45637</v>
+        <v>45477</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45596</v>
+        <v>45582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45327</v>
+        <v>45477</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>0.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45956</v>
+        <v>46157</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45582</v>
+        <v>45637</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45477</v>
+        <v>44592</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46157</v>
+        <v>45596</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44592</v>
+        <v>45956</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45415</v>
+        <v>46272</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2438,7 +2438,7 @@
         <v>45582</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2511,7 +2511,7 @@
         <v>45477</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 35770-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46272</v>
+        <v>46264</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45596</v>
+        <v>45415</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>6.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2713,7 +2713,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35770-2026</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46264</v>
+        <v>44867</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45795</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44865</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,16 +1041,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>30.3</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1074,49 +1074,49 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,17 +1146,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>14.1</v>
+        <v>30.3</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1179,49 +1179,49 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46038</v>
+        <v>45795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>14.1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1409,14 +1409,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45795</v>
+        <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45415</v>
+        <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7.7</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45327</v>
+        <v>45596</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45477</v>
+        <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1708,7 +1708,7 @@
         <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45582</v>
+        <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45477</v>
+        <v>45956</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1927,7 +1927,7 @@
         <v>46157</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45637</v>
+        <v>44592</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44592</v>
+        <v>45415</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45596</v>
+        <v>45582</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45956</v>
+        <v>45582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46272</v>
+        <v>45477</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2365,7 +2365,7 @@
         <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45582</v>
+        <v>46272</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 35770-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45477</v>
+        <v>46264</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35770-2026</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46264</v>
+        <v>45415</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>6.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45415</v>
+        <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2713,7 +2713,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2723,14 +2723,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44867</v>
+        <v>45795</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45795</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44865</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>46038</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>45795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>45596</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45956</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>46157</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>44592</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>45415</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45582</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45477</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>46272</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>46264</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45415</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>45795</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45795</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44865</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>46038</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>45795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>45596</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>45327</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45956</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>46157</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>44592</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>45415</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45582</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45477</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>46272</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>46264</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45415</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>44867</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>45795</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45795</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>44865</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>46038</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>45795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45637</v>
+        <v>45415</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1489,7 +1489,7 @@
         <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45596</v>
+        <v>45582</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45327</v>
+        <v>45582</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45582</v>
+        <v>45477</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45477</v>
+        <v>45956</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45956</v>
+        <v>45327</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1927,7 +1927,7 @@
         <v>46157</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44592</v>
+        <v>45637</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45415</v>
+        <v>44592</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.7</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45596</v>
+        <v>45477</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 35770-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46272</v>
+        <v>46264</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35770-2026</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46264</v>
+        <v>45415</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>6.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45415</v>
+        <v>44867</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2650,14 +2650,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44867</v>
+        <v>45795</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2713,7 +2713,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2723,14 +2723,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45795</v>
+        <v>46272</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 270-2025</t>
+          <t>A 24088-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -702,14 +702,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45660</v>
+        <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>8.9</v>
+        <v>2.8</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -761,152 +761,152 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Tusengömming
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 270-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45660</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SOTENÄS</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsalm
 Skogsödla</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 24088-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45795</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SOTENÄS</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Tusengömming
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 50239-2022</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44865</v>
+        <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>13.2</v>
+        <v>30.3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -945,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -963,55 +963,55 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46038</v>
+        <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>14.1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1081,42 +1081,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,16 +1146,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>30.3</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1179,49 +1179,49 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 50239-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45795</v>
+        <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1251,20 +1251,20 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.1</v>
+        <v>13.2</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45415</v>
+        <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7.7</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1489,7 +1489,7 @@
         <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45582</v>
+        <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45582</v>
+        <v>44867</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1701,14 +1701,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45477</v>
+        <v>45795</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45956</v>
+        <v>45596</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>45327</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46157</v>
+        <v>45956</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45637</v>
+        <v>45582</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44592</v>
+        <v>45477</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45596</v>
+        <v>46157</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45596</v>
+        <v>44592</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45582</v>
+        <v>45415</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>7.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35770-2026</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46264</v>
+        <v>45582</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45415</v>
+        <v>45477</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44867</v>
+        <v>45596</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 35770-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2650,14 +2650,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45795</v>
+        <v>46264</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>46272</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45660</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>46038</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45637</v>
+        <v>45415</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45477</v>
+        <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45415</v>
+        <v>44867</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44867</v>
+        <v>45477</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>45795</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45596</v>
+        <v>45582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45327</v>
+        <v>45582</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1927,7 +1927,7 @@
         <v>45956</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45582</v>
+        <v>45477</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45477</v>
+        <v>45327</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2146,7 +2146,7 @@
         <v>46157</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44592</v>
+        <v>45637</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45415</v>
+        <v>44592</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.7</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45596</v>
+        <v>45477</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2657,7 +2657,7 @@
         <v>46264</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>46272</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 24088-2025</t>
+          <t>A 270-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -702,14 +702,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45795</v>
+        <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.8</v>
+        <v>8.9</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -761,152 +761,152 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsalm
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 24088-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45795</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SOTENÄS</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Ask
 Tusengömming
 Blåsippa</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 270-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45660</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SOTENÄS</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsalm
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,16 +936,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>30.3</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -969,49 +969,49 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1028,7 +1028,7 @@
         <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,17 +1041,17 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>14.1</v>
+        <v>30.3</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1074,49 +1074,49 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46038</v>
+        <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>14.1</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1186,35 +1186,35 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45415</v>
+        <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7.7</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1482,14 +1482,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45415</v>
+        <v>45795</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44867</v>
+        <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.3</v>
+        <v>7.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1701,14 +1701,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45795</v>
+        <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45582</v>
+        <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.8</v>
+        <v>0.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45582</v>
+        <v>45477</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45956</v>
+        <v>45596</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45477</v>
+        <v>45956</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45327</v>
+        <v>46157</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46157</v>
+        <v>45596</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45637</v>
+        <v>45327</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44592</v>
+        <v>45415</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>6.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45596</v>
+        <v>44867</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45596</v>
+        <v>46272</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2511,7 +2511,7 @@
         <v>45582</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2584,7 +2584,7 @@
         <v>45477</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2657,7 +2657,7 @@
         <v>46264</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46272</v>
+        <v>44592</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 270-2025</t>
+          <t>A 24088-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -702,14 +702,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45660</v>
+        <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>8.9</v>
+        <v>2.8</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -761,152 +761,152 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Tusengömming
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 270-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45660</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SOTENÄS</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsalm
 Skogsödla</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 24088-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45795</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SOTENÄS</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Tusengömming
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46038</v>
+        <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,17 +936,17 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>30.3</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -969,49 +969,49 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,16 +1041,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>30.3</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1074,42 +1074,42 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45637</v>
+        <v>45596</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1482,14 +1482,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45795</v>
+        <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45415</v>
+        <v>45956</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>7.7</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45582</v>
+        <v>45596</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1708,7 +1708,7 @@
         <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45477</v>
+        <v>45415</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45596</v>
+        <v>44867</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1993,14 +1993,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45956</v>
+        <v>45795</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 35770-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46157</v>
+        <v>46264</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45596</v>
+        <v>45477</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45327</v>
+        <v>46272</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45415</v>
+        <v>45582</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.2</v>
+        <v>2.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44867</v>
+        <v>45582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46272</v>
+        <v>46157</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45582</v>
+        <v>45477</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45477</v>
+        <v>45327</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.4</v>
+        <v>4.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35770-2026</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46264</v>
+        <v>45637</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>44592</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45660</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>46038</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45596</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>45956</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>45596</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45415</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>44867</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45795</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>46264</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45477</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>46272</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45582</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>45582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>46157</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45477</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45327</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>45637</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>44592</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45660</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>46038</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>45596</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45415</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>45956</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>45596</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>45582</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>45415</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>44867</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45795</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>46264</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45477</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>46272</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>45582</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>45582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>46157</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45477</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45327</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>45637</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>44592</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 24088-2025</t>
+          <t>A 270-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -702,14 +702,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45795</v>
+        <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.8</v>
+        <v>8.9</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -761,145 +761,145 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsalm
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 24088-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45795</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SOTENÄS</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Ask
 Tusengömming
 Blåsippa</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 270-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45660</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SOTENÄS</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsalm
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
         <v/>
       </c>
     </row>
@@ -923,7 +923,7 @@
         <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46038</v>
+        <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>14.1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1081,42 +1081,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>14.1</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1186,35 +1186,35 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
         <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45596</v>
+        <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45415</v>
+        <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7.7</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
         <v>45956</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>45596</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45582</v>
+        <v>45415</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45477</v>
+        <v>44867</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.2</v>
+        <v>3.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45415</v>
+        <v>45327</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1920,14 +1920,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44867</v>
+        <v>45795</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1993,14 +1993,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45795</v>
+        <v>45582</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 35770-2026</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46264</v>
+        <v>45477</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45477</v>
+        <v>44592</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46272</v>
+        <v>46157</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45582</v>
+        <v>45415</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.8</v>
+        <v>7.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2365,7 +2365,7 @@
         <v>45582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46157</v>
+        <v>45582</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 35770-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45477</v>
+        <v>46264</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45327</v>
+        <v>45477</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.5</v>
+        <v>0.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45637</v>
+        <v>45596</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2713,7 +2713,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44592</v>
+        <v>46272</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>45795</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 50239-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45795</v>
+        <v>44865</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>30.3</v>
+        <v>13.2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -945,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -963,55 +963,55 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>14.1</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1081,42 +1081,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46038</v>
+        <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,17 +1146,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>30.3</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1179,49 +1179,49 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50239-2022</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44865</v>
+        <v>45795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45637</v>
+        <v>45596</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45956</v>
+        <v>45415</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>7.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45596</v>
+        <v>45477</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45415</v>
+        <v>45477</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44867</v>
+        <v>45477</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>45327</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1920,14 +1920,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45795</v>
+        <v>45956</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2000,7 +2000,7 @@
         <v>45582</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44592</v>
+        <v>45415</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>6.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46157</v>
+        <v>44867</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45415</v>
+        <v>45637</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.7</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45582</v>
+        <v>44592</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 35770-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45582</v>
+        <v>46264</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35770-2026</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46264</v>
+        <v>45596</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2577,14 +2577,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45477</v>
+        <v>45795</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45596</v>
+        <v>46272</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46272</v>
+        <v>46157</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 270-2025</t>
+          <t>A 24088-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -702,14 +702,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45660</v>
+        <v>45795</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>8.9</v>
+        <v>2.8</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -761,152 +761,152 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Tusengömming
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 270-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45660</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SOTENÄS</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsalm
 Skogsödla</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 24088-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45795</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SOTENÄS</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Tusengömming
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 50239-2022</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44865</v>
+        <v>45795</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>13.2</v>
+        <v>30.3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -945,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -963,55 +963,55 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46038</v>
+        <v>45795</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>14.1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1081,42 +1081,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,16 +1146,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>30.3</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1179,49 +1179,49 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 50239-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45795</v>
+        <v>44865</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1251,20 +1251,20 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.1</v>
+        <v>13.2</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45596</v>
+        <v>45415</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45582</v>
+        <v>44867</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45415</v>
+        <v>44592</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>7.7</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1618,7 +1618,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 24086-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1628,14 +1628,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45477</v>
+        <v>45795</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45477</v>
+        <v>45637</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45477</v>
+        <v>45415</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>7.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45327</v>
+        <v>45582</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45956</v>
+        <v>45582</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45582</v>
+        <v>45956</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45582</v>
+        <v>45477</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45415</v>
+        <v>45477</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6.2</v>
+        <v>0.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44867</v>
+        <v>46157</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45637</v>
+        <v>45596</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44592</v>
+        <v>45596</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35770-2026</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46264</v>
+        <v>45327</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 35770-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45596</v>
+        <v>46264</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 24086-2025</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2577,14 +2577,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45795</v>
+        <v>45582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 36765-2026</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46272</v>
+        <v>45477</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2713,7 +2713,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 36765-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46157</v>
+        <v>46272</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>

--- a/Översikt SOTENÄS.xlsx
+++ b/Översikt SOTENÄS.xlsx
@@ -601,7 +601,7 @@
         <v>45795</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 24088-2025</t>
+          <t>A 270-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -702,14 +702,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45795</v>
+        <v>45660</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.8</v>
+        <v>8.9</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -731,13 +731,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -761,152 +761,152 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsalm
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="X3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="Y3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AA3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A 24088-2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45795</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SOTENÄS</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Ask
 Tusengömming
 Blåsippa</t>
         </is>
       </c>
-      <c r="W3">
+      <c r="W4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24088-2025 artfynd.xlsx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="X3">
+      <c r="X4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24088-2025 karta.png", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24088-2025 georefererad karta.tif", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24088-2025 FSC-klagomål.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24088-2025 FSC-klagomål mail.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24088-2025 tillsynsbegäran.docx", "A 24088-2025")</f>
         <v/>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24088-2025 tillsynsbegäran mail.docx", "A 24088-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A 270-2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45660</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46324</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>SOTENÄS</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsalm
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 270-2025 artfynd.xlsx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 270-2025 karta.png", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 270-2025 georefererad karta.tif", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 270-2025 FSC-klagomål.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 270-2025 FSC-klagomål mail.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 270-2025 tillsynsbegäran.docx", "A 270-2025")</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 270-2025 tillsynsbegäran mail.docx", "A 270-2025")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 24087-2025</t>
+          <t>A 2980-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45795</v>
+        <v>46038</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -936,16 +936,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>30.3</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -969,49 +969,49 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 23503-2025</t>
+          <t>A 50239-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45795</v>
+        <v>44865</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1041,20 +1041,20 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>14.1</v>
+        <v>13.2</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
@@ -1065,10 +1065,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1081,42 +1081,42 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Blockskapania</t>
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2980-2026</t>
+          <t>A 24087-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46038</v>
+        <v>45795</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1146,17 +1146,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>30.3</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1179,49 +1179,49 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödlånke</t>
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 2980-2026 artfynd.xlsx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 24087-2025 artfynd.xlsx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 2980-2026 karta.png", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 24087-2025 karta.png", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 2980-2026 georefererad karta.tif", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 24087-2025 georefererad karta.tif", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 2980-2026 FSC-klagomål.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 24087-2025 FSC-klagomål.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 2980-2026 FSC-klagomål mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 24087-2025 FSC-klagomål mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 2980-2026 tillsynsbegäran.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 24087-2025 tillsynsbegäran.docx", "A 24087-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 2980-2026 tillsynsbegäran mail.docx", "A 2980-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 24087-2025 tillsynsbegäran mail.docx", "A 24087-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50239-2022</t>
+          <t>A 23503-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44865</v>
+        <v>45795</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1275,10 +1275,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1291,35 +1291,35 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blockskapania</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 50239-2022 artfynd.xlsx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/artfynd/A 23503-2025 artfynd.xlsx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 50239-2022 karta.png", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor/A 23503-2025 karta.png", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 50239-2022 georefererad karta.tif", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/kartor_geotiff/A 23503-2025 georefererad karta.tif", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 50239-2022 FSC-klagomål.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomål/A 23503-2025 FSC-klagomål.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 50239-2022 FSC-klagomål mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/klagomålsmail/A 23503-2025 FSC-klagomål mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 50239-2022 tillsynsbegäran.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsyn/A 23503-2025 tillsynsbegäran.docx", "A 23503-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 50239-2022 tillsynsbegäran mail.docx", "A 50239-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1427/tillsynsmail/A 23503-2025 tillsynsbegäran mail.docx", "A 23503-2025")</f>
         <v/>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         <v>44886</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 17491-2024</t>
+          <t>A 59231-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45415</v>
+        <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 50864-2022</t>
+          <t>A 28416-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44867</v>
+        <v>45477</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 4780-2022</t>
+          <t>A 49633-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44592</v>
+        <v>45596</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1635,7 +1635,7 @@
         <v>45795</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 59231-2024</t>
+          <t>A 4422-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45637</v>
+        <v>45327</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 17492-2024</t>
+          <t>A 46579-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45415</v>
+        <v>45582</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.7</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 46587-2024</t>
+          <t>A 52960-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45582</v>
+        <v>45956</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46588-2024</t>
+          <t>A 28409-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45582</v>
+        <v>45477</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 52960-2025</t>
+          <t>A 4780-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45956</v>
+        <v>44592</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28418-2024</t>
+          <t>A 17492-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45477</v>
+        <v>45415</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.2</v>
+        <v>7.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28416-2024</t>
+          <t>A 46587-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45477</v>
+        <v>45582</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 22789-2026</t>
+          <t>A 46588-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46157</v>
+        <v>45582</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 49634-2024</t>
+          <t>A 22789-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45596</v>
+        <v>46157</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49633-2024</t>
+          <t>A 28418-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45596</v>
+        <v>45477</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4422-2024</t>
+          <t>A 49634-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45327</v>
+        <v>45596</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35770-2026</t>
+          <t>A 17491-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46264</v>
+        <v>45415</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>6.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 46579-2024</t>
+          <t>A 50864-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45582</v>
+        <v>44867</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28409-2024</t>
+          <t>A 35770-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45477</v>
+        <v>46264</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>46272</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45890</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
